--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY220"/>
+  <dimension ref="A1:AY223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26613,6 +26613,302 @@
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>125917029</v>
+      </c>
+      <c r="B221" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Mörtsjökojan, Mörtsjökojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>560164</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6977137</v>
+      </c>
+      <c r="S221" t="n">
+        <v>20</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>125923615</v>
+      </c>
+      <c r="B222" t="n">
+        <v>78419</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>772</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Elfenbenslav</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Heterodermia speciosa</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>(Wulfen) Trevis.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Ilvåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>560079</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6977049</v>
+      </c>
+      <c r="S222" t="n">
+        <v>25</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Sydostvänd lodyta, fjädermossor växer intill</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>125923616</v>
+      </c>
+      <c r="B223" t="n">
+        <v>41429</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>100453</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Baptria tibiale</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(Esper, 1790)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Ilvåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>560122</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6977064</v>
+      </c>
+      <c r="S223" t="n">
+        <v>25</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>125923615</v>
       </c>
       <c r="B222" t="n">
-        <v>78419</v>
+        <v>78420</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>125923615</v>
       </c>
       <c r="B222" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>125923615</v>
       </c>
       <c r="B222" t="n">
-        <v>78424</v>
+        <v>78425</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>125923616</v>
       </c>
       <c r="B223" t="n">
-        <v>41429</v>
+        <v>41430</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>125923615</v>
       </c>
       <c r="B222" t="n">
-        <v>78425</v>
+        <v>78429</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2020 artfynd.xlsx
+++ b/artfynd/A 39058-2020 artfynd.xlsx
@@ -26618,7 +26618,7 @@
         <v>125917029</v>
       </c>
       <c r="B221" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>125923615</v>
       </c>
       <c r="B222" t="n">
-        <v>78429</v>
+        <v>78432</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>125923616</v>
       </c>
       <c r="B223" t="n">
-        <v>41430</v>
+        <v>41431</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
